--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.46034016237222</v>
+        <v>8.037305276385485</v>
       </c>
       <c r="D2" t="n">
-        <v>47.09488985418822</v>
+        <v>7.652919601305586</v>
       </c>
       <c r="E2" t="n">
-        <v>16.57215566887069</v>
+        <v>2.692975296191486</v>
       </c>
       <c r="F2" t="n">
-        <v>17.76697113028827</v>
+        <v>2.887132808671843</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.70535421495642</v>
+        <v>2.714620059930418</v>
       </c>
       <c r="D3" t="n">
-        <v>15.98621799479914</v>
+        <v>2.597760424154861</v>
       </c>
       <c r="E3" t="n">
-        <v>16.57215566887069</v>
+        <v>2.692975296191486</v>
       </c>
       <c r="F3" t="n">
-        <v>17.76697113028827</v>
+        <v>2.887132808671843</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.55773366339235</v>
+        <v>8.378131720301257</v>
       </c>
       <c r="D4" t="n">
-        <v>8.072789774428225</v>
+        <v>1.311828338344587</v>
       </c>
       <c r="E4" t="n">
-        <v>16.57215566887069</v>
+        <v>2.692975296191486</v>
       </c>
       <c r="F4" t="n">
-        <v>17.76697113028827</v>
+        <v>2.887132808671843</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.53606734593282</v>
+        <v>8.699610943714084</v>
       </c>
       <c r="D5" t="n">
-        <v>5.463619342074667</v>
+        <v>0.8878381430871334</v>
       </c>
       <c r="E5" t="n">
-        <v>16.57215566887069</v>
+        <v>2.692975296191486</v>
       </c>
       <c r="F5" t="n">
-        <v>17.76697113028827</v>
+        <v>2.887132808671843</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.68374357730138</v>
+        <v>7.911108331311474</v>
       </c>
       <c r="D6" t="n">
-        <v>46.17970549622591</v>
+        <v>7.504202143136712</v>
       </c>
       <c r="E6" t="n">
-        <v>16.57215566887069</v>
+        <v>2.692975296191486</v>
       </c>
       <c r="F6" t="n">
-        <v>17.76697113028827</v>
+        <v>2.887132808671843</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.04694222535925</v>
+        <v>1.632628111620878</v>
       </c>
       <c r="D7" t="n">
-        <v>8.629365196038473</v>
+        <v>1.402271844356252</v>
       </c>
       <c r="E7" t="n">
-        <v>16.57215566887069</v>
+        <v>2.692975296191486</v>
       </c>
       <c r="F7" t="n">
-        <v>17.76697113028827</v>
+        <v>2.887132808671843</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.86511012725388</v>
+        <v>6.965580395678756</v>
       </c>
       <c r="D8" t="n">
-        <v>41.01197900115518</v>
+        <v>6.664446587687716</v>
       </c>
       <c r="E8" t="n">
-        <v>16.57215566887069</v>
+        <v>2.692975296191486</v>
       </c>
       <c r="F8" t="n">
-        <v>17.76697113028827</v>
+        <v>2.887132808671843</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
